--- a/simulations/PARETO/Résultat avec contrainte/CO2_HH.xlsx
+++ b/simulations/PARETO/Résultat avec contrainte/CO2_HH.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hravoaha\Desktop\Thèse\Thèse 2023\Objectif 2\biowaste_optim\simulations\PARETO\Résultat avec contrainte\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A8CCBEB-A88A-49EA-BC39-DF58877F1159}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2F01E77-9117-491C-B300-2B021290E9AA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7750" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="results" sheetId="1" r:id="rId1"/>
@@ -3094,60 +3094,200 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="results"/>
-      <sheetName val="Feuil1"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
-        <row r="2">
-          <cell r="AD2" t="str">
-            <v>Carbon</v>
-          </cell>
-          <cell r="AH2" t="str">
-            <v>HHssC</v>
-          </cell>
-        </row>
         <row r="3">
+          <cell r="B3" t="str">
+            <v>1.0</v>
+          </cell>
+          <cell r="C3">
+            <v>0.6</v>
+          </cell>
+          <cell r="D3">
+            <v>0.37</v>
+          </cell>
+          <cell r="E3">
+            <v>2.52</v>
+          </cell>
+          <cell r="I3">
+            <v>1.29</v>
+          </cell>
+          <cell r="X3">
+            <v>2.3199999999999998</v>
+          </cell>
           <cell r="AD3">
+            <v>93.51</v>
+          </cell>
+          <cell r="AK3">
             <v>-203340.0842835083</v>
           </cell>
-          <cell r="AH3">
+          <cell r="AL3">
+            <v>-479894.37340540468</v>
+          </cell>
+          <cell r="AM3">
+            <v>-3.5317706843912799</v>
+          </cell>
+          <cell r="AN3">
+            <v>-190007.86677072401</v>
+          </cell>
+          <cell r="AO3">
             <v>0.36546878935102339</v>
           </cell>
         </row>
         <row r="4">
-          <cell r="AD4">
-            <v>-271684.9677193996</v>
-          </cell>
-          <cell r="AH4">
-            <v>0.4149897620013091</v>
+          <cell r="B4" t="str">
+            <v>2.0</v>
+          </cell>
+          <cell r="C4">
+            <v>0.6</v>
+          </cell>
+          <cell r="D4">
+            <v>0.37</v>
+          </cell>
+          <cell r="E4">
+            <v>2.52</v>
+          </cell>
+          <cell r="I4">
+            <v>1.29</v>
+          </cell>
+          <cell r="X4">
+            <v>2.3199999999999998</v>
+          </cell>
+          <cell r="AJ4">
+            <v>93.51</v>
+          </cell>
+          <cell r="AK4">
+            <v>-596910.37483729084</v>
+          </cell>
+          <cell r="AL4">
+            <v>-675655.61481981387</v>
+          </cell>
+          <cell r="AM4">
+            <v>-6.3501085548001077</v>
+          </cell>
+          <cell r="AN4">
+            <v>-157626.13086978649</v>
+          </cell>
+          <cell r="AO4">
+            <v>0.6218076245490981</v>
           </cell>
         </row>
         <row r="5">
-          <cell r="AD5">
-            <v>-271684.9677193996</v>
+          <cell r="B5" t="str">
+            <v>3.0</v>
+          </cell>
+          <cell r="C5">
+            <v>0.6</v>
+          </cell>
+          <cell r="D5">
+            <v>0.37</v>
+          </cell>
+          <cell r="E5">
+            <v>2.52</v>
+          </cell>
+          <cell r="I5">
+            <v>1.29</v>
+          </cell>
+          <cell r="X5">
+            <v>2.3199999999999998</v>
           </cell>
           <cell r="AH5">
-            <v>0.4149897620013091</v>
+            <v>93.51</v>
+          </cell>
+          <cell r="AK5">
+            <v>-651101.69874275709</v>
+          </cell>
+          <cell r="AL5">
+            <v>-479036.53667522129</v>
+          </cell>
+          <cell r="AM5">
+            <v>-5.0996868266494699</v>
+          </cell>
+          <cell r="AN5">
+            <v>-34562.503224742322</v>
+          </cell>
+          <cell r="AO5">
+            <v>0.88092441684732015</v>
           </cell>
         </row>
         <row r="6">
-          <cell r="AD6">
-            <v>-544740.82515175932</v>
+          <cell r="B6" t="str">
+            <v>4.0</v>
+          </cell>
+          <cell r="C6">
+            <v>0.6</v>
+          </cell>
+          <cell r="D6">
+            <v>0.37</v>
+          </cell>
+          <cell r="E6">
+            <v>2.52</v>
+          </cell>
+          <cell r="I6">
+            <v>1.29</v>
+          </cell>
+          <cell r="X6">
+            <v>2.3199999999999998</v>
           </cell>
           <cell r="AH6">
-            <v>2.2999443118901919</v>
+            <v>93.51</v>
+          </cell>
+          <cell r="AK6">
+            <v>-651101.69874275709</v>
+          </cell>
+          <cell r="AL6">
+            <v>-479036.53667522129</v>
+          </cell>
+          <cell r="AM6">
+            <v>-5.0996868266494699</v>
+          </cell>
+          <cell r="AN6">
+            <v>-34562.503224742322</v>
+          </cell>
+          <cell r="AO6">
+            <v>0.88092441684732015</v>
           </cell>
         </row>
         <row r="7">
-          <cell r="AD7">
-            <v>-544740.82515175932</v>
+          <cell r="B7" t="str">
+            <v>5.0</v>
+          </cell>
+          <cell r="C7">
+            <v>0.6</v>
+          </cell>
+          <cell r="D7">
+            <v>0.37</v>
+          </cell>
+          <cell r="E7">
+            <v>2.52</v>
+          </cell>
+          <cell r="I7">
+            <v>1.29</v>
+          </cell>
+          <cell r="X7">
+            <v>2.3199999999999998</v>
           </cell>
           <cell r="AH7">
-            <v>2.2999443118901919</v>
+            <v>93.51</v>
+          </cell>
+          <cell r="AK7">
+            <v>-651101.69874275709</v>
+          </cell>
+          <cell r="AL7">
+            <v>-479036.53667522129</v>
+          </cell>
+          <cell r="AM7">
+            <v>-5.0996868266494699</v>
+          </cell>
+          <cell r="AN7">
+            <v>-34562.503224742322</v>
+          </cell>
+          <cell r="AO7">
+            <v>0.88092441684732015</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3158,200 +3298,60 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="results"/>
+      <sheetName val="Feuil1"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
+        <row r="2">
+          <cell r="AD2" t="str">
+            <v>Carbon</v>
+          </cell>
+          <cell r="AH2" t="str">
+            <v>HHssC</v>
+          </cell>
+        </row>
         <row r="3">
-          <cell r="B3" t="str">
-            <v>1.0</v>
-          </cell>
-          <cell r="C3">
-            <v>0.6</v>
-          </cell>
-          <cell r="D3">
-            <v>0.37</v>
-          </cell>
-          <cell r="E3">
-            <v>2.52</v>
-          </cell>
-          <cell r="I3">
-            <v>1.29</v>
-          </cell>
-          <cell r="X3">
-            <v>2.3199999999999998</v>
-          </cell>
           <cell r="AD3">
-            <v>93.51</v>
-          </cell>
-          <cell r="AK3">
             <v>-203340.0842835083</v>
           </cell>
-          <cell r="AL3">
-            <v>-479894.37340540468</v>
-          </cell>
-          <cell r="AM3">
-            <v>-3.5317706843912799</v>
-          </cell>
-          <cell r="AN3">
-            <v>-190007.86677072401</v>
-          </cell>
-          <cell r="AO3">
+          <cell r="AH3">
             <v>0.36546878935102339</v>
           </cell>
         </row>
         <row r="4">
-          <cell r="B4" t="str">
-            <v>2.0</v>
-          </cell>
-          <cell r="C4">
-            <v>0.6</v>
-          </cell>
-          <cell r="D4">
-            <v>0.37</v>
-          </cell>
-          <cell r="E4">
-            <v>2.52</v>
-          </cell>
-          <cell r="I4">
-            <v>1.29</v>
-          </cell>
-          <cell r="X4">
-            <v>2.3199999999999998</v>
-          </cell>
-          <cell r="AJ4">
-            <v>93.51</v>
-          </cell>
-          <cell r="AK4">
-            <v>-596910.37483729084</v>
-          </cell>
-          <cell r="AL4">
-            <v>-675655.61481981387</v>
-          </cell>
-          <cell r="AM4">
-            <v>-6.3501085548001077</v>
-          </cell>
-          <cell r="AN4">
-            <v>-157626.13086978649</v>
-          </cell>
-          <cell r="AO4">
-            <v>0.6218076245490981</v>
+          <cell r="AD4">
+            <v>-271684.9677193996</v>
+          </cell>
+          <cell r="AH4">
+            <v>0.4149897620013091</v>
           </cell>
         </row>
         <row r="5">
-          <cell r="B5" t="str">
-            <v>3.0</v>
-          </cell>
-          <cell r="C5">
-            <v>0.6</v>
-          </cell>
-          <cell r="D5">
-            <v>0.37</v>
-          </cell>
-          <cell r="E5">
-            <v>2.52</v>
-          </cell>
-          <cell r="I5">
-            <v>1.29</v>
-          </cell>
-          <cell r="X5">
-            <v>2.3199999999999998</v>
+          <cell r="AD5">
+            <v>-271684.9677193996</v>
           </cell>
           <cell r="AH5">
-            <v>93.51</v>
-          </cell>
-          <cell r="AK5">
-            <v>-651101.69874275709</v>
-          </cell>
-          <cell r="AL5">
-            <v>-479036.53667522129</v>
-          </cell>
-          <cell r="AM5">
-            <v>-5.0996868266494699</v>
-          </cell>
-          <cell r="AN5">
-            <v>-34562.503224742322</v>
-          </cell>
-          <cell r="AO5">
-            <v>0.88092441684732015</v>
+            <v>0.4149897620013091</v>
           </cell>
         </row>
         <row r="6">
-          <cell r="B6" t="str">
-            <v>4.0</v>
-          </cell>
-          <cell r="C6">
-            <v>0.6</v>
-          </cell>
-          <cell r="D6">
-            <v>0.37</v>
-          </cell>
-          <cell r="E6">
-            <v>2.52</v>
-          </cell>
-          <cell r="I6">
-            <v>1.29</v>
-          </cell>
-          <cell r="X6">
-            <v>2.3199999999999998</v>
+          <cell r="AD6">
+            <v>-544740.82515175932</v>
           </cell>
           <cell r="AH6">
-            <v>93.51</v>
-          </cell>
-          <cell r="AK6">
-            <v>-651101.69874275709</v>
-          </cell>
-          <cell r="AL6">
-            <v>-479036.53667522129</v>
-          </cell>
-          <cell r="AM6">
-            <v>-5.0996868266494699</v>
-          </cell>
-          <cell r="AN6">
-            <v>-34562.503224742322</v>
-          </cell>
-          <cell r="AO6">
-            <v>0.88092441684732015</v>
+            <v>2.2999443118901919</v>
           </cell>
         </row>
         <row r="7">
-          <cell r="B7" t="str">
-            <v>5.0</v>
-          </cell>
-          <cell r="C7">
-            <v>0.6</v>
-          </cell>
-          <cell r="D7">
-            <v>0.37</v>
-          </cell>
-          <cell r="E7">
-            <v>2.52</v>
-          </cell>
-          <cell r="I7">
-            <v>1.29</v>
-          </cell>
-          <cell r="X7">
-            <v>2.3199999999999998</v>
+          <cell r="AD7">
+            <v>-544740.82515175932</v>
           </cell>
           <cell r="AH7">
-            <v>93.51</v>
-          </cell>
-          <cell r="AK7">
-            <v>-651101.69874275709</v>
-          </cell>
-          <cell r="AL7">
-            <v>-479036.53667522129</v>
-          </cell>
-          <cell r="AM7">
-            <v>-5.0996868266494699</v>
-          </cell>
-          <cell r="AN7">
-            <v>-34562.503224742322</v>
-          </cell>
-          <cell r="AO7">
-            <v>0.88092441684732015</v>
+            <v>2.2999443118901919</v>
           </cell>
         </row>
       </sheetData>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3856,163 +3856,163 @@
         <v>0</v>
       </c>
       <c r="B3" t="str">
-        <f>[2]results!B3</f>
+        <f>[1]results!B3</f>
         <v>1.0</v>
       </c>
       <c r="C3">
-        <f>[2]results!C3</f>
+        <f>[1]results!C3</f>
         <v>0.6</v>
       </c>
       <c r="D3" s="3">
-        <f>[2]results!D3</f>
+        <f>[1]results!D3</f>
         <v>0.37</v>
       </c>
       <c r="E3">
-        <f>[2]results!E3</f>
+        <f>[1]results!E3</f>
         <v>2.52</v>
       </c>
       <c r="F3">
-        <f>[2]results!F3</f>
+        <f>[1]results!F3</f>
         <v>0</v>
       </c>
       <c r="G3">
-        <f>[2]results!G3</f>
+        <f>[1]results!G3</f>
         <v>0</v>
       </c>
       <c r="H3">
-        <f>[2]results!H3</f>
+        <f>[1]results!H3</f>
         <v>0</v>
       </c>
       <c r="I3">
-        <f>[2]results!I3</f>
+        <f>[1]results!I3</f>
         <v>1.29</v>
       </c>
       <c r="J3">
-        <f>[2]results!J3</f>
+        <f>[1]results!J3</f>
         <v>0</v>
       </c>
       <c r="K3">
-        <f>[2]results!K3</f>
+        <f>[1]results!K3</f>
         <v>0</v>
       </c>
       <c r="L3">
-        <f>[2]results!L3</f>
+        <f>[1]results!L3</f>
         <v>0</v>
       </c>
       <c r="M3">
-        <f>[2]results!M3</f>
+        <f>[1]results!M3</f>
         <v>0</v>
       </c>
       <c r="N3">
-        <f>[2]results!N3</f>
+        <f>[1]results!N3</f>
         <v>0</v>
       </c>
       <c r="O3">
-        <f>[2]results!O3</f>
+        <f>[1]results!O3</f>
         <v>0</v>
       </c>
       <c r="P3">
-        <f>[2]results!P3</f>
+        <f>[1]results!P3</f>
         <v>0</v>
       </c>
       <c r="Q3">
-        <f>[2]results!Q3</f>
+        <f>[1]results!Q3</f>
         <v>0</v>
       </c>
       <c r="R3">
-        <f>[2]results!R3</f>
+        <f>[1]results!R3</f>
         <v>0</v>
       </c>
       <c r="S3">
-        <f>[2]results!S3</f>
+        <f>[1]results!S3</f>
         <v>0</v>
       </c>
       <c r="T3">
-        <f>[2]results!T3</f>
+        <f>[1]results!T3</f>
         <v>0</v>
       </c>
       <c r="U3">
-        <f>[2]results!U3</f>
+        <f>[1]results!U3</f>
         <v>0</v>
       </c>
       <c r="V3">
-        <f>[2]results!V3</f>
+        <f>[1]results!V3</f>
         <v>0</v>
       </c>
       <c r="W3">
-        <f>[2]results!W3</f>
+        <f>[1]results!W3</f>
         <v>0</v>
       </c>
       <c r="X3">
-        <f>[2]results!X3</f>
+        <f>[1]results!X3</f>
         <v>2.3199999999999998</v>
       </c>
       <c r="Y3">
-        <f>[2]results!Y3</f>
+        <f>[1]results!Y3</f>
         <v>0</v>
       </c>
       <c r="Z3">
-        <f>[2]results!Z3</f>
+        <f>[1]results!Z3</f>
         <v>0</v>
       </c>
       <c r="AA3">
-        <f>[2]results!AA3</f>
+        <f>[1]results!AA3</f>
         <v>0</v>
       </c>
       <c r="AB3">
-        <f>[2]results!AB3</f>
+        <f>[1]results!AB3</f>
         <v>0</v>
       </c>
       <c r="AC3">
-        <f>[2]results!AC3</f>
+        <f>[1]results!AC3</f>
         <v>0</v>
       </c>
       <c r="AD3" s="3">
-        <f>[2]results!AD3</f>
+        <f>[1]results!AD3</f>
         <v>93.51</v>
       </c>
       <c r="AE3">
-        <f>[2]results!AE3</f>
+        <f>[1]results!AE3</f>
         <v>0</v>
       </c>
       <c r="AF3">
-        <f>[2]results!AF3</f>
+        <f>[1]results!AF3</f>
         <v>0</v>
       </c>
       <c r="AG3">
-        <f>[2]results!AG3</f>
+        <f>[1]results!AG3</f>
         <v>0</v>
       </c>
       <c r="AH3">
-        <f>[2]results!AH3</f>
+        <f>[1]results!AH3</f>
         <v>0</v>
       </c>
       <c r="AI3">
-        <f>[2]results!AI3</f>
+        <f>[1]results!AI3</f>
         <v>0</v>
       </c>
       <c r="AJ3">
-        <f>[2]results!AJ3</f>
+        <f>[1]results!AJ3</f>
         <v>0</v>
       </c>
       <c r="AK3" s="4">
-        <f>[2]results!AK3</f>
+        <f>[1]results!AK3</f>
         <v>-203340.0842835083</v>
       </c>
       <c r="AL3" s="4">
-        <f>[2]results!AL3</f>
+        <f>[1]results!AL3</f>
         <v>-479894.37340540468</v>
       </c>
       <c r="AM3" s="4">
-        <f>[2]results!AM3</f>
+        <f>[1]results!AM3</f>
         <v>-3.5317706843912799</v>
       </c>
       <c r="AN3" s="4">
-        <f>[2]results!AN3</f>
+        <f>[1]results!AN3</f>
         <v>-190007.86677072401</v>
       </c>
       <c r="AO3" s="4">
-        <f>[2]results!AO3</f>
+        <f>[1]results!AO3</f>
         <v>0.36546878935102339</v>
       </c>
       <c r="AQ3">
@@ -4056,163 +4056,163 @@
         <v>1</v>
       </c>
       <c r="B4" t="str">
-        <f>[2]results!B4</f>
+        <f>[1]results!B4</f>
         <v>2.0</v>
       </c>
       <c r="C4">
-        <f>[2]results!C4</f>
+        <f>[1]results!C4</f>
         <v>0.6</v>
       </c>
       <c r="D4" s="3">
-        <f>[2]results!D4</f>
+        <f>[1]results!D4</f>
         <v>0.37</v>
       </c>
       <c r="E4">
-        <f>[2]results!E4</f>
+        <f>[1]results!E4</f>
         <v>2.52</v>
       </c>
       <c r="F4">
-        <f>[2]results!F4</f>
+        <f>[1]results!F4</f>
         <v>0</v>
       </c>
       <c r="G4">
-        <f>[2]results!G4</f>
+        <f>[1]results!G4</f>
         <v>0</v>
       </c>
       <c r="H4">
-        <f>[2]results!H4</f>
+        <f>[1]results!H4</f>
         <v>0</v>
       </c>
       <c r="I4">
-        <f>[2]results!I4</f>
+        <f>[1]results!I4</f>
         <v>1.29</v>
       </c>
       <c r="J4">
-        <f>[2]results!J4</f>
+        <f>[1]results!J4</f>
         <v>0</v>
       </c>
       <c r="K4">
-        <f>[2]results!K4</f>
+        <f>[1]results!K4</f>
         <v>0</v>
       </c>
       <c r="L4">
-        <f>[2]results!L4</f>
+        <f>[1]results!L4</f>
         <v>0</v>
       </c>
       <c r="M4">
-        <f>[2]results!M4</f>
+        <f>[1]results!M4</f>
         <v>0</v>
       </c>
       <c r="N4">
-        <f>[2]results!N4</f>
+        <f>[1]results!N4</f>
         <v>0</v>
       </c>
       <c r="O4">
-        <f>[2]results!O4</f>
+        <f>[1]results!O4</f>
         <v>0</v>
       </c>
       <c r="P4">
-        <f>[2]results!P4</f>
+        <f>[1]results!P4</f>
         <v>0</v>
       </c>
       <c r="Q4">
-        <f>[2]results!Q4</f>
+        <f>[1]results!Q4</f>
         <v>0</v>
       </c>
       <c r="R4">
-        <f>[2]results!R4</f>
+        <f>[1]results!R4</f>
         <v>0</v>
       </c>
       <c r="S4">
-        <f>[2]results!S4</f>
+        <f>[1]results!S4</f>
         <v>0</v>
       </c>
       <c r="T4">
-        <f>[2]results!T4</f>
+        <f>[1]results!T4</f>
         <v>0</v>
       </c>
       <c r="U4">
-        <f>[2]results!U4</f>
+        <f>[1]results!U4</f>
         <v>0</v>
       </c>
       <c r="V4">
-        <f>[2]results!V4</f>
+        <f>[1]results!V4</f>
         <v>0</v>
       </c>
       <c r="W4">
-        <f>[2]results!W4</f>
+        <f>[1]results!W4</f>
         <v>0</v>
       </c>
       <c r="X4">
-        <f>[2]results!X4</f>
+        <f>[1]results!X4</f>
         <v>2.3199999999999998</v>
       </c>
       <c r="Y4">
-        <f>[2]results!Y4</f>
+        <f>[1]results!Y4</f>
         <v>0</v>
       </c>
       <c r="Z4">
-        <f>[2]results!Z4</f>
+        <f>[1]results!Z4</f>
         <v>0</v>
       </c>
       <c r="AA4">
-        <f>[2]results!AA4</f>
+        <f>[1]results!AA4</f>
         <v>0</v>
       </c>
       <c r="AB4">
-        <f>[2]results!AB4</f>
+        <f>[1]results!AB4</f>
         <v>0</v>
       </c>
       <c r="AC4">
-        <f>[2]results!AC4</f>
+        <f>[1]results!AC4</f>
         <v>0</v>
       </c>
       <c r="AD4">
-        <f>[2]results!AD4</f>
+        <f>[1]results!AD4</f>
         <v>0</v>
       </c>
       <c r="AE4">
-        <f>[2]results!AE4</f>
+        <f>[1]results!AE4</f>
         <v>0</v>
       </c>
       <c r="AF4">
-        <f>[2]results!AF4</f>
+        <f>[1]results!AF4</f>
         <v>0</v>
       </c>
       <c r="AG4">
-        <f>[2]results!AG4</f>
+        <f>[1]results!AG4</f>
         <v>0</v>
       </c>
       <c r="AH4">
-        <f>[2]results!AH4</f>
+        <f>[1]results!AH4</f>
         <v>0</v>
       </c>
       <c r="AI4">
-        <f>[2]results!AI4</f>
+        <f>[1]results!AI4</f>
         <v>0</v>
       </c>
       <c r="AJ4" s="3">
-        <f>[2]results!AJ4</f>
+        <f>[1]results!AJ4</f>
         <v>93.51</v>
       </c>
       <c r="AK4" s="4">
-        <f>[2]results!AK4</f>
+        <f>[1]results!AK4</f>
         <v>-596910.37483729084</v>
       </c>
       <c r="AL4" s="4">
-        <f>[2]results!AL4</f>
+        <f>[1]results!AL4</f>
         <v>-675655.61481981387</v>
       </c>
       <c r="AM4" s="4">
-        <f>[2]results!AM4</f>
+        <f>[1]results!AM4</f>
         <v>-6.3501085548001077</v>
       </c>
       <c r="AN4" s="4">
-        <f>[2]results!AN4</f>
+        <f>[1]results!AN4</f>
         <v>-157626.13086978649</v>
       </c>
       <c r="AO4" s="4">
-        <f>[2]results!AO4</f>
+        <f>[1]results!AO4</f>
         <v>0.6218076245490981</v>
       </c>
       <c r="AQ4">
@@ -4256,163 +4256,163 @@
         <v>2</v>
       </c>
       <c r="B5" t="str">
-        <f>[2]results!B5</f>
+        <f>[1]results!B5</f>
         <v>3.0</v>
       </c>
       <c r="C5">
-        <f>[2]results!C5</f>
+        <f>[1]results!C5</f>
         <v>0.6</v>
       </c>
       <c r="D5" s="3">
-        <f>[2]results!D5</f>
+        <f>[1]results!D5</f>
         <v>0.37</v>
       </c>
       <c r="E5">
-        <f>[2]results!E5</f>
+        <f>[1]results!E5</f>
         <v>2.52</v>
       </c>
       <c r="F5">
-        <f>[2]results!F5</f>
+        <f>[1]results!F5</f>
         <v>0</v>
       </c>
       <c r="G5">
-        <f>[2]results!G5</f>
+        <f>[1]results!G5</f>
         <v>0</v>
       </c>
       <c r="H5">
-        <f>[2]results!H5</f>
+        <f>[1]results!H5</f>
         <v>0</v>
       </c>
       <c r="I5">
-        <f>[2]results!I5</f>
+        <f>[1]results!I5</f>
         <v>1.29</v>
       </c>
       <c r="J5">
-        <f>[2]results!J5</f>
+        <f>[1]results!J5</f>
         <v>0</v>
       </c>
       <c r="K5">
-        <f>[2]results!K5</f>
+        <f>[1]results!K5</f>
         <v>0</v>
       </c>
       <c r="L5">
-        <f>[2]results!L5</f>
+        <f>[1]results!L5</f>
         <v>0</v>
       </c>
       <c r="M5">
-        <f>[2]results!M5</f>
+        <f>[1]results!M5</f>
         <v>0</v>
       </c>
       <c r="N5">
-        <f>[2]results!N5</f>
+        <f>[1]results!N5</f>
         <v>0</v>
       </c>
       <c r="O5">
-        <f>[2]results!O5</f>
+        <f>[1]results!O5</f>
         <v>0</v>
       </c>
       <c r="P5">
-        <f>[2]results!P5</f>
+        <f>[1]results!P5</f>
         <v>0</v>
       </c>
       <c r="Q5">
-        <f>[2]results!Q5</f>
+        <f>[1]results!Q5</f>
         <v>0</v>
       </c>
       <c r="R5">
-        <f>[2]results!R5</f>
+        <f>[1]results!R5</f>
         <v>0</v>
       </c>
       <c r="S5">
-        <f>[2]results!S5</f>
+        <f>[1]results!S5</f>
         <v>0</v>
       </c>
       <c r="T5">
-        <f>[2]results!T5</f>
+        <f>[1]results!T5</f>
         <v>0</v>
       </c>
       <c r="U5">
-        <f>[2]results!U5</f>
+        <f>[1]results!U5</f>
         <v>0</v>
       </c>
       <c r="V5">
-        <f>[2]results!V5</f>
+        <f>[1]results!V5</f>
         <v>0</v>
       </c>
       <c r="W5">
-        <f>[2]results!W5</f>
+        <f>[1]results!W5</f>
         <v>0</v>
       </c>
       <c r="X5">
-        <f>[2]results!X5</f>
+        <f>[1]results!X5</f>
         <v>2.3199999999999998</v>
       </c>
       <c r="Y5">
-        <f>[2]results!Y5</f>
+        <f>[1]results!Y5</f>
         <v>0</v>
       </c>
       <c r="Z5">
-        <f>[2]results!Z5</f>
+        <f>[1]results!Z5</f>
         <v>0</v>
       </c>
       <c r="AA5">
-        <f>[2]results!AA5</f>
+        <f>[1]results!AA5</f>
         <v>0</v>
       </c>
       <c r="AB5">
-        <f>[2]results!AB5</f>
+        <f>[1]results!AB5</f>
         <v>0</v>
       </c>
       <c r="AC5">
-        <f>[2]results!AC5</f>
+        <f>[1]results!AC5</f>
         <v>0</v>
       </c>
       <c r="AD5">
-        <f>[2]results!AD5</f>
+        <f>[1]results!AD5</f>
         <v>0</v>
       </c>
       <c r="AE5">
-        <f>[2]results!AE5</f>
+        <f>[1]results!AE5</f>
         <v>0</v>
       </c>
       <c r="AF5">
-        <f>[2]results!AF5</f>
+        <f>[1]results!AF5</f>
         <v>0</v>
       </c>
       <c r="AG5">
-        <f>[2]results!AG5</f>
+        <f>[1]results!AG5</f>
         <v>0</v>
       </c>
       <c r="AH5">
-        <f>[2]results!AH5</f>
+        <f>[1]results!AH5</f>
         <v>93.51</v>
       </c>
       <c r="AI5">
-        <f>[2]results!AI5</f>
+        <f>[1]results!AI5</f>
         <v>0</v>
       </c>
       <c r="AJ5" s="3">
-        <f>[2]results!AJ5</f>
+        <f>[1]results!AJ5</f>
         <v>0</v>
       </c>
       <c r="AK5" s="4">
-        <f>[2]results!AK5</f>
+        <f>[1]results!AK5</f>
         <v>-651101.69874275709</v>
       </c>
       <c r="AL5" s="4">
-        <f>[2]results!AL5</f>
+        <f>[1]results!AL5</f>
         <v>-479036.53667522129</v>
       </c>
       <c r="AM5" s="4">
-        <f>[2]results!AM5</f>
+        <f>[1]results!AM5</f>
         <v>-5.0996868266494699</v>
       </c>
       <c r="AN5" s="4">
-        <f>[2]results!AN5</f>
+        <f>[1]results!AN5</f>
         <v>-34562.503224742322</v>
       </c>
       <c r="AO5" s="4">
-        <f>[2]results!AO5</f>
+        <f>[1]results!AO5</f>
         <v>0.88092441684732015</v>
       </c>
       <c r="AQ5">
@@ -4456,163 +4456,163 @@
         <v>3</v>
       </c>
       <c r="B6" t="str">
-        <f>[2]results!B6</f>
+        <f>[1]results!B6</f>
         <v>4.0</v>
       </c>
       <c r="C6">
-        <f>[2]results!C6</f>
+        <f>[1]results!C6</f>
         <v>0.6</v>
       </c>
       <c r="D6" s="3">
-        <f>[2]results!D6</f>
+        <f>[1]results!D6</f>
         <v>0.37</v>
       </c>
       <c r="E6">
-        <f>[2]results!E6</f>
+        <f>[1]results!E6</f>
         <v>2.52</v>
       </c>
       <c r="F6">
-        <f>[2]results!F6</f>
+        <f>[1]results!F6</f>
         <v>0</v>
       </c>
       <c r="G6">
-        <f>[2]results!G6</f>
+        <f>[1]results!G6</f>
         <v>0</v>
       </c>
       <c r="H6">
-        <f>[2]results!H6</f>
+        <f>[1]results!H6</f>
         <v>0</v>
       </c>
       <c r="I6">
-        <f>[2]results!I6</f>
+        <f>[1]results!I6</f>
         <v>1.29</v>
       </c>
       <c r="J6">
-        <f>[2]results!J6</f>
+        <f>[1]results!J6</f>
         <v>0</v>
       </c>
       <c r="K6">
-        <f>[2]results!K6</f>
+        <f>[1]results!K6</f>
         <v>0</v>
       </c>
       <c r="L6">
-        <f>[2]results!L6</f>
+        <f>[1]results!L6</f>
         <v>0</v>
       </c>
       <c r="M6">
-        <f>[2]results!M6</f>
+        <f>[1]results!M6</f>
         <v>0</v>
       </c>
       <c r="N6">
-        <f>[2]results!N6</f>
+        <f>[1]results!N6</f>
         <v>0</v>
       </c>
       <c r="O6">
-        <f>[2]results!O6</f>
+        <f>[1]results!O6</f>
         <v>0</v>
       </c>
       <c r="P6">
-        <f>[2]results!P6</f>
+        <f>[1]results!P6</f>
         <v>0</v>
       </c>
       <c r="Q6">
-        <f>[2]results!Q6</f>
+        <f>[1]results!Q6</f>
         <v>0</v>
       </c>
       <c r="R6">
-        <f>[2]results!R6</f>
+        <f>[1]results!R6</f>
         <v>0</v>
       </c>
       <c r="S6">
-        <f>[2]results!S6</f>
+        <f>[1]results!S6</f>
         <v>0</v>
       </c>
       <c r="T6">
-        <f>[2]results!T6</f>
+        <f>[1]results!T6</f>
         <v>0</v>
       </c>
       <c r="U6">
-        <f>[2]results!U6</f>
+        <f>[1]results!U6</f>
         <v>0</v>
       </c>
       <c r="V6">
-        <f>[2]results!V6</f>
+        <f>[1]results!V6</f>
         <v>0</v>
       </c>
       <c r="W6">
-        <f>[2]results!W6</f>
+        <f>[1]results!W6</f>
         <v>0</v>
       </c>
       <c r="X6">
-        <f>[2]results!X6</f>
+        <f>[1]results!X6</f>
         <v>2.3199999999999998</v>
       </c>
       <c r="Y6">
-        <f>[2]results!Y6</f>
+        <f>[1]results!Y6</f>
         <v>0</v>
       </c>
       <c r="Z6">
-        <f>[2]results!Z6</f>
+        <f>[1]results!Z6</f>
         <v>0</v>
       </c>
       <c r="AA6">
-        <f>[2]results!AA6</f>
+        <f>[1]results!AA6</f>
         <v>0</v>
       </c>
       <c r="AB6">
-        <f>[2]results!AB6</f>
+        <f>[1]results!AB6</f>
         <v>0</v>
       </c>
       <c r="AC6">
-        <f>[2]results!AC6</f>
+        <f>[1]results!AC6</f>
         <v>0</v>
       </c>
       <c r="AD6">
-        <f>[2]results!AD6</f>
+        <f>[1]results!AD6</f>
         <v>0</v>
       </c>
       <c r="AE6">
-        <f>[2]results!AE6</f>
+        <f>[1]results!AE6</f>
         <v>0</v>
       </c>
       <c r="AF6">
-        <f>[2]results!AF6</f>
+        <f>[1]results!AF6</f>
         <v>0</v>
       </c>
       <c r="AG6">
-        <f>[2]results!AG6</f>
+        <f>[1]results!AG6</f>
         <v>0</v>
       </c>
       <c r="AH6">
-        <f>[2]results!AH6</f>
+        <f>[1]results!AH6</f>
         <v>93.51</v>
       </c>
       <c r="AI6">
-        <f>[2]results!AI6</f>
+        <f>[1]results!AI6</f>
         <v>0</v>
       </c>
       <c r="AJ6" s="3">
-        <f>[2]results!AJ6</f>
+        <f>[1]results!AJ6</f>
         <v>0</v>
       </c>
       <c r="AK6" s="4">
-        <f>[2]results!AK6</f>
+        <f>[1]results!AK6</f>
         <v>-651101.69874275709</v>
       </c>
       <c r="AL6" s="4">
-        <f>[2]results!AL6</f>
+        <f>[1]results!AL6</f>
         <v>-479036.53667522129</v>
       </c>
       <c r="AM6" s="4">
-        <f>[2]results!AM6</f>
+        <f>[1]results!AM6</f>
         <v>-5.0996868266494699</v>
       </c>
       <c r="AN6" s="4">
-        <f>[2]results!AN6</f>
+        <f>[1]results!AN6</f>
         <v>-34562.503224742322</v>
       </c>
       <c r="AO6" s="4">
-        <f>[2]results!AO6</f>
+        <f>[1]results!AO6</f>
         <v>0.88092441684732015</v>
       </c>
       <c r="AQ6">
@@ -4656,163 +4656,163 @@
         <v>4</v>
       </c>
       <c r="B7" t="str">
-        <f>[2]results!B7</f>
+        <f>[1]results!B7</f>
         <v>5.0</v>
       </c>
       <c r="C7">
-        <f>[2]results!C7</f>
+        <f>[1]results!C7</f>
         <v>0.6</v>
       </c>
       <c r="D7" s="3">
-        <f>[2]results!D7</f>
+        <f>[1]results!D7</f>
         <v>0.37</v>
       </c>
       <c r="E7">
-        <f>[2]results!E7</f>
+        <f>[1]results!E7</f>
         <v>2.52</v>
       </c>
       <c r="F7">
-        <f>[2]results!F7</f>
+        <f>[1]results!F7</f>
         <v>0</v>
       </c>
       <c r="G7">
-        <f>[2]results!G7</f>
+        <f>[1]results!G7</f>
         <v>0</v>
       </c>
       <c r="H7">
-        <f>[2]results!H7</f>
+        <f>[1]results!H7</f>
         <v>0</v>
       </c>
       <c r="I7">
-        <f>[2]results!I7</f>
+        <f>[1]results!I7</f>
         <v>1.29</v>
       </c>
       <c r="J7">
-        <f>[2]results!J7</f>
+        <f>[1]results!J7</f>
         <v>0</v>
       </c>
       <c r="K7">
-        <f>[2]results!K7</f>
+        <f>[1]results!K7</f>
         <v>0</v>
       </c>
       <c r="L7">
-        <f>[2]results!L7</f>
+        <f>[1]results!L7</f>
         <v>0</v>
       </c>
       <c r="M7">
-        <f>[2]results!M7</f>
+        <f>[1]results!M7</f>
         <v>0</v>
       </c>
       <c r="N7">
-        <f>[2]results!N7</f>
+        <f>[1]results!N7</f>
         <v>0</v>
       </c>
       <c r="O7">
-        <f>[2]results!O7</f>
+        <f>[1]results!O7</f>
         <v>0</v>
       </c>
       <c r="P7">
-        <f>[2]results!P7</f>
+        <f>[1]results!P7</f>
         <v>0</v>
       </c>
       <c r="Q7">
-        <f>[2]results!Q7</f>
+        <f>[1]results!Q7</f>
         <v>0</v>
       </c>
       <c r="R7">
-        <f>[2]results!R7</f>
+        <f>[1]results!R7</f>
         <v>0</v>
       </c>
       <c r="S7">
-        <f>[2]results!S7</f>
+        <f>[1]results!S7</f>
         <v>0</v>
       </c>
       <c r="T7">
-        <f>[2]results!T7</f>
+        <f>[1]results!T7</f>
         <v>0</v>
       </c>
       <c r="U7">
-        <f>[2]results!U7</f>
+        <f>[1]results!U7</f>
         <v>0</v>
       </c>
       <c r="V7">
-        <f>[2]results!V7</f>
+        <f>[1]results!V7</f>
         <v>0</v>
       </c>
       <c r="W7">
-        <f>[2]results!W7</f>
+        <f>[1]results!W7</f>
         <v>0</v>
       </c>
       <c r="X7">
-        <f>[2]results!X7</f>
+        <f>[1]results!X7</f>
         <v>2.3199999999999998</v>
       </c>
       <c r="Y7">
-        <f>[2]results!Y7</f>
+        <f>[1]results!Y7</f>
         <v>0</v>
       </c>
       <c r="Z7">
-        <f>[2]results!Z7</f>
+        <f>[1]results!Z7</f>
         <v>0</v>
       </c>
       <c r="AA7">
-        <f>[2]results!AA7</f>
+        <f>[1]results!AA7</f>
         <v>0</v>
       </c>
       <c r="AB7">
-        <f>[2]results!AB7</f>
+        <f>[1]results!AB7</f>
         <v>0</v>
       </c>
       <c r="AC7">
-        <f>[2]results!AC7</f>
+        <f>[1]results!AC7</f>
         <v>0</v>
       </c>
       <c r="AD7">
-        <f>[2]results!AD7</f>
+        <f>[1]results!AD7</f>
         <v>0</v>
       </c>
       <c r="AE7">
-        <f>[2]results!AE7</f>
+        <f>[1]results!AE7</f>
         <v>0</v>
       </c>
       <c r="AF7">
-        <f>[2]results!AF7</f>
+        <f>[1]results!AF7</f>
         <v>0</v>
       </c>
       <c r="AG7">
-        <f>[2]results!AG7</f>
+        <f>[1]results!AG7</f>
         <v>0</v>
       </c>
       <c r="AH7">
-        <f>[2]results!AH7</f>
+        <f>[1]results!AH7</f>
         <v>93.51</v>
       </c>
       <c r="AI7">
-        <f>[2]results!AI7</f>
+        <f>[1]results!AI7</f>
         <v>0</v>
       </c>
       <c r="AJ7" s="3">
-        <f>[2]results!AJ7</f>
+        <f>[1]results!AJ7</f>
         <v>0</v>
       </c>
       <c r="AK7" s="4">
-        <f>[2]results!AK7</f>
+        <f>[1]results!AK7</f>
         <v>-651101.69874275709</v>
       </c>
       <c r="AL7" s="4">
-        <f>[2]results!AL7</f>
+        <f>[1]results!AL7</f>
         <v>-479036.53667522129</v>
       </c>
       <c r="AM7" s="4">
-        <f>[2]results!AM7</f>
+        <f>[1]results!AM7</f>
         <v>-5.0996868266494699</v>
       </c>
       <c r="AN7" s="4">
-        <f>[2]results!AN7</f>
+        <f>[1]results!AN7</f>
         <v>-34562.503224742322</v>
       </c>
       <c r="AO7" s="4">
-        <f>[2]results!AO7</f>
+        <f>[1]results!AO7</f>
         <v>0.88092441684732015</v>
       </c>
       <c r="AQ7">
@@ -4997,11 +4997,11 @@
         <v>HHssC</v>
       </c>
       <c r="D2" t="str">
-        <f>[1]results!AD2</f>
+        <f>[2]results!AD2</f>
         <v>Carbon</v>
       </c>
       <c r="E2" t="str">
-        <f>[1]results!AH2</f>
+        <f>[2]results!AH2</f>
         <v>HHssC</v>
       </c>
     </row>
@@ -5018,11 +5018,11 @@
         <v>0.36546878935102339</v>
       </c>
       <c r="D3">
-        <f>[1]results!AD3</f>
+        <f>[2]results!AD3</f>
         <v>-203340.0842835083</v>
       </c>
       <c r="E3">
-        <f>[1]results!AH3</f>
+        <f>[2]results!AH3</f>
         <v>0.36546878935102339</v>
       </c>
     </row>
@@ -5039,11 +5039,11 @@
         <v>0.6218076245490981</v>
       </c>
       <c r="D4">
-        <f>[1]results!AD4</f>
+        <f>[2]results!AD4</f>
         <v>-271684.9677193996</v>
       </c>
       <c r="E4">
-        <f>[1]results!AH4</f>
+        <f>[2]results!AH4</f>
         <v>0.4149897620013091</v>
       </c>
     </row>
@@ -5060,11 +5060,11 @@
         <v>0.88092441684732015</v>
       </c>
       <c r="D5">
-        <f>[1]results!AD5</f>
+        <f>[2]results!AD5</f>
         <v>-271684.9677193996</v>
       </c>
       <c r="E5">
-        <f>[1]results!AH5</f>
+        <f>[2]results!AH5</f>
         <v>0.4149897620013091</v>
       </c>
     </row>
@@ -5081,11 +5081,11 @@
         <v>0.88092441684732015</v>
       </c>
       <c r="D6">
-        <f>[1]results!AD6</f>
+        <f>[2]results!AD6</f>
         <v>-544740.82515175932</v>
       </c>
       <c r="E6">
-        <f>[1]results!AH6</f>
+        <f>[2]results!AH6</f>
         <v>2.2999443118901919</v>
       </c>
     </row>
@@ -5102,11 +5102,11 @@
         <v>0.88092441684732015</v>
       </c>
       <c r="D7">
-        <f>[1]results!AD7</f>
+        <f>[2]results!AD7</f>
         <v>-544740.82515175932</v>
       </c>
       <c r="E7">
-        <f>[1]results!AH7</f>
+        <f>[2]results!AH7</f>
         <v>2.2999443118901919</v>
       </c>
     </row>
